--- a/ModdingKit/package/LangMod/EN/ModViewerLang.xlsx
+++ b/ModdingKit/package/LangMod/EN/ModViewerLang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\GameMods\Elin.Plugins\ModdingKit\package\LangMod\EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D000B633-AEE7-449E-8F88-507DF7ED2C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B71DEA-B926-4128-A6D8-158C371DEC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
   <si>
     <t>id</t>
   </si>
@@ -419,6 +419,15 @@
   </si>
   <si>
     <t>Made for #1 (current mod API #2)</t>
+  </si>
+  <si>
+    <t>mod_info_workshop</t>
+  </si>
+  <si>
+    <t>Open workshop page</t>
+  </si>
+  <si>
+    <t>ワークショップページを開く</t>
   </si>
 </sst>
 </file>
@@ -790,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,6 +1292,17 @@
         <v>129</v>
       </c>
     </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
